--- a/assets/2026年进口货物物流跟踪表-铁矿协作一部&新拓.xlsx
+++ b/assets/2026年进口货物物流跟踪表-铁矿协作一部&新拓.xlsx
@@ -1259,7 +1259,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2035,6 +2035,9 @@
     <xf numFmtId="164" fontId="13" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6450,7 +6453,6 @@
     <mergeCell ref="V27:V33"/>
     <mergeCell ref="AI10:AI15"/>
     <mergeCell ref="AX34:AX41"/>
-    <mergeCell ref="K6:K9"/>
     <mergeCell ref="AS10:AS15"/>
     <mergeCell ref="AG2:AG5"/>
     <mergeCell ref="AU10:AU15"/>
@@ -6496,6 +6498,7 @@
     <mergeCell ref="AT6:AT9"/>
     <mergeCell ref="AX10:AX15"/>
     <mergeCell ref="Z34:Z41"/>
+    <mergeCell ref="Z10:Z15"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="P27:P33"/>
@@ -6541,7 +6544,7 @@
     <mergeCell ref="I6:I9"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="U27:U33"/>
-    <mergeCell ref="Z10:Z15"/>
+    <mergeCell ref="K6:K9"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="AG27:AG33"/>
   </mergeCells>
@@ -9017,8 +9020,16 @@
           <t>SF5198886201009</t>
         </is>
       </c>
-      <c r="AV22" s="84" t="n"/>
-      <c r="AW22" s="84" t="n"/>
+      <c r="AV22" s="267" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
+      <c r="AW22" s="267" t="inlineStr">
+        <is>
+          <t>已归档</t>
+        </is>
+      </c>
       <c r="AX22" s="84" t="n"/>
       <c r="AY22" s="84" t="n"/>
       <c r="AZ22" s="84" t="n"/>
